--- a/stories/arbres/ATOM-SAN.HYG.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, Léa se lève. Papa est dans la salle de bain. Léa prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Léa rit un peu. Le soir, c'est pareil. Léa prend sa brosse. Un adulte est avec elle. C'est papa. Ils brossent ensemble. Léa dit : matin et soir. Papa dit : oui, avec moi. Les dents sont propres. Léa range la brosse.</t>
+          <t>Le matin, Léa se lève. Papa est dans la salle de bain. Léa prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Léa rit un peu. Le soir, c'est pareil. Léa prend sa brosse. Un adulte est avec elle. C'est papa. Ils brossent ensemble. Matin et soir. Oui, avec moi. Les dents sont propres. Léa range la brosse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Léa se lève. Papa est dans la salle de bain. Léa prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Léa rit un peu. Le soir, c'est pareil. Léa prend sa brosse. Un adulte est avec elle. C'est papa. Ils brossent ensemble.
+enfant-f|Matin et soir.
+papa|Oui, avec moi.
+narrateur|Les dents sont propres. Léa range la brosse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Léa se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Léa se rince la bouche. Elle dit merci à papa. Les dents brillent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|Les dents sont propres. Léa range la brosse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Léa se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Léa a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Léa se rince la bouche. Elle dit merci à papa. Les dents brillent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La brosse de Léa</t>
+          <t>La brosse de Victorina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La veilleuse fait un rond orange. Victorina prend sa brosse avec papa, le matin puis le soir. Les dents brillent.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, Léa se lève. Papa est dans la salle de bain. Léa prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Léa rit un peu. Le soir, c'est pareil. Léa prend sa brosse. Un adulte est avec elle. C'est papa. Ils brossent ensemble. Matin et soir. Oui, avec moi. Les dents sont propres. Léa range la brosse.</t>
+          <t>La petite veilleuse fait un rond orange. La lune est encore à la fenêtre. Le pyjama à étoiles est sur la chaise. Ça sent le café, tout loin. Le tapis de la salle de bain est doux. Un oiseau dit un petit cri. Victorina, viens. L'eau est prête. J'arrive, papa. Tu vois le rond orange ? Oui. La veilleuse. En ce moment, Victorina se lève. Elle rejoint papa. Papa est dans la salle de bain. L'eau coule un peu. Prends ta brosse. Ma brosse. Victorina prend sa brosse. Papa prend la sienne. Un adulte est avec elle. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça chatouille un peu. Oui. On brosse ensemble. Victorina rit un peu. Elle se rince. L'eau est fraîche. Elle range la brosse. Bravo. Tu as fait du bon travail. C'est le matin. On a brossé. Avec toi. Oui. Avec un adulte. Plus tard, le soir arrive. La veilleuse se rallume. La lune est plus ronde. Victorina, viens. C'est le soir. Ma brosse. Victorina prend sa brosse. Un adulte est avec elle. C'est papa. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec moi. Avec un adulte. Les dents sont propres. Victorina range la brosse. Tu as fini de brosser ? Oui, papa. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le matin, Léa se lève. Papa est dans la salle de bain. Léa prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Léa rit un peu. Le soir, c'est pareil. Léa prend sa brosse. Un adulte est avec elle. C'est papa. Ils brossent ensemble.
+          <t>narrateur|La petite veilleuse fait un rond orange.
+narrateur|La lune est encore à la fenêtre.
+narrateur|Le pyjama à étoiles est sur la chaise.
+narrateur|Ça sent le café, tout loin.
+narrateur|Le tapis de la salle de bain est doux.
+narrateur|Un oiseau dit un petit cri.
+papa|Victorina, viens. L'eau est prête.
+enfant-f|J'arrive, papa.
+papa|Tu vois le rond orange ?
+enfant-f|Oui. La veilleuse.
+narrateur|En ce moment, Victorina se lève.
+narrateur|Elle rejoint papa.
+narrateur|Papa est dans la salle de bain.
+narrateur|L'eau coule un peu.
+papa|Prends ta brosse.
+enfant-f|Ma brosse.
+narrateur|Victorina prend sa brosse.
+narrateur|Papa prend la sienne.
+narrateur|Un adulte est avec elle.
+narrateur|C'est papa.
+narrateur|Ils se brossent les dents.
+narrateur|La brosse va en haut.
+narrateur|La brosse va en bas.
+enfant-f|Ça chatouille un peu.
+papa|Oui. On brosse ensemble.
+narrateur|Victorina rit un peu.
+narrateur|Elle se rince.
+narrateur|L'eau est fraîche.
+narrateur|Elle range la brosse.
+papa|Bravo. Tu as fait du bon travail.
+papa|C'est le matin. On a brossé.
+enfant-f|Avec toi.
+papa|Oui. Avec un adulte.
+narrateur|Plus tard, le soir arrive.
+narrateur|La veilleuse se rallume.
+narrateur|La lune est plus ronde.
+papa|Victorina, viens. C'est le soir.
+enfant-f|Ma brosse.
+narrateur|Victorina prend sa brosse.
+narrateur|Un adulte est avec elle.
+narrateur|C'est papa.
+narrateur|Ils brossent ensemble.
+narrateur|La brosse va en haut.
+narrateur|La brosse va en bas.
 enfant-f|Matin et soir.
 papa|Oui, avec moi.
-narrateur|Les dents sont propres. Léa range la brosse.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Avec un adulte.
+narrateur|Les dents sont propres.
+narrateur|Victorina range la brosse.
+papa|Tu as fini de brosser ?
+enfant-f|Oui, papa.
+papa|Bravo, Victorina.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Léa se brosse les dents. Avec quoi ?</t>
+          <t>Victorina se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,10 +1562,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Léa se brosse les dents. Avec quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorina se brosse les dents.
+narrateur|Avec quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1531,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir.</t>
+          <t>Victorina a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir. Tu te souviens ? Matin et soir. Oui. Avec papa. Bravo. C'est le bon geste. La veilleuse fait encore son rond. Le pyjama à étoiles attend.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,10 +1734,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorina a pris la brosse.
+narrateur|Elle brosse avec l'adulte.
+narrateur|C'est papa.
+narrateur|Matin et soir.
+papa|Tu te souviens ? Matin et soir.
+enfant-f|Oui. Avec papa.
+papa|Bravo. C'est le bon geste.
+narrateur|La veilleuse fait encore son rond.
+narrateur|Le pyjama à étoiles attend.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1703,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Léa se rince la bouche. Elle dit merci à papa. Les dents brillent.</t>
+          <t>Victorina se rince la bouche. L'eau est fraîche. Merci, papa. Tes dents brillent. Tu as fini ? Oui. Bravo. On va au lit. Le pyjama à étoiles l'attend. La lune est à la fenêtre. Le tapis est encore doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,10 +1905,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Léa se rince la bouche. Elle dit merci à papa. Les dents brillent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Victorina se rince la bouche.
+narrateur|L'eau est fraîche.
+enfant-f|Merci, papa.
+papa|Tes dents brillent.
+papa|Tu as fini ?
+enfant-f|Oui.
+papa|Bravo. On va au lit.
+narrateur|Le pyjama à étoiles l'attend.
+narrateur|La lune est à la fenêtre.
+narrateur|Le tapis est encore doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,7 +1941,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a brossé le matin. Victorina a brossé le soir. Avec papa. Avec la brosse. Bravo, Victorina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,10 +2081,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Victorina a brossé le matin.
+narrateur|Victorina a brossé le soir.
+narrateur|Avec papa. Avec la brosse.
+papa|Bravo, Victorina.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La petite veilleuse fait un rond orange. La lune est encore à la fenêtre. Le pyjama à étoiles est sur la chaise. Ça sent le café, tout loin. Le tapis de la salle de bain est doux. Un oiseau dit un petit cri. Victorina, viens. L'eau est prête. J'arrive, papa. Tu vois le rond orange ? Oui. La veilleuse. En ce moment, Victorina se lève. Elle rejoint papa. Papa est dans la salle de bain. L'eau coule un peu. Prends ta brosse. Ma brosse. Victorina prend sa brosse. Papa prend la sienne. Un adulte est avec elle. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça chatouille un peu. Oui. On brosse ensemble. Victorina rit un peu. Elle se rince. L'eau est fraîche. Elle range la brosse. Bravo. Tu as fait du bon travail. C'est le matin. On a brossé. Avec toi. Oui. Avec un adulte. Plus tard, le soir arrive. La veilleuse se rallume. La lune est plus ronde. Victorina, viens. C'est le soir. Ma brosse. Victorina prend sa brosse. Un adulte est avec elle. C'est papa. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec moi. Avec un adulte. Les dents sont propres. Victorina range la brosse. Tu as fini de brosser ? Oui, papa. Bravo, Victorina.</t>
+          <t>La petite veilleuse fait un rond orange. La lune est encore à la fenêtre. Le pyjama à étoiles est sur la chaise. Ça sent le café, tout loin. Le tapis de la salle de bain est doux. Un oiseau dit un petit cri. Victorina, viens. L'eau est prête. J'arrive, papa. Tu vois le rond orange ? Oui. La veilleuse. En ce moment, Victorina se lève. Elle rejoint papa. Papa est dans la salle de bain. L'eau coule un peu. Prends ta brosse. Ma brosse. Victorina prend sa brosse. Papa prend la sienne. Un adulte est avec elle. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça chatouille un peu. Oui. On brosse ensemble. Victorina rit un peu. Elle se rince. L'eau est fraîche. Elle range la brosse. Le matin, on a brossé. Avec toi. Oui. Avec un adulte. Victorina regarde le miroir. Ses dents sont propres. Elles brillent un peu. Oui. Bravo. Plus tard, le soir arrive. La veilleuse se rallume. La lune est plus ronde. Victorina, viens. C'est le soir. Ma brosse. Victorina prend sa brosse. Un adulte est avec elle. C'est papa. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec moi. Avec un adulte. Les dents sont propres. Victorina range la brosse. Tu as fini de brosser ? Oui, papa. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;matin&lt;/emphasis&gt;, Léa se lève. Papa est dans la salle de bain. Léa prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Léa rit un peu. Le soir, c'est pareil. Léa prend sa brosse. Un adulte est avec elle. C'est papa. Ils brossent ensemble. Léa dit : matin et soir. Papa dit : oui, avec moi. Les dents sont propres. Léa range la brosse.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La petite veilleuse fait un rond orange. La lune est encore à la fenêtre. Le pyjama à étoiles est sur la chaise. Ça sent le café, tout loin. Le tapis de la salle de bain est doux. Un oiseau dit un petit cri. Victorina, viens. L'eau est prête. J'arrive, papa. Tu vois le rond orange ? Oui. La veilleuse. En ce moment, Victorina se lève. Elle rejoint papa. Papa est dans la salle de bain. L'eau coule un peu. Prends ta brosse. Ma brosse. Victorina prend sa brosse. Papa prend la sienne. Un adulte est avec elle. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça chatouille un peu. Oui. On brosse ensemble. Victorina rit un peu. Elle se rince. L'eau est fraîche. Elle range la brosse. Le matin, on a brossé. Avec toi. Oui. Avec un adulte. Victorina regarde le miroir. Ses dents sont propres. Elles brillent un peu. Oui. Bravo. Plus tard, le soir arrive. La veilleuse se rallume. La lune est plus ronde. Victorina, viens. C'est le soir. Ma brosse. Victorina prend sa brosse. Un adulte est avec elle. C'est papa. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec moi. Avec un adulte. Les dents sont propres. Victorina range la brosse. Tu as fini de brosser ? Oui, papa. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1353,10 +1353,13 @@
 narrateur|Elle se rince.
 narrateur|L'eau est fraîche.
 narrateur|Elle range la brosse.
-papa|Bravo. Tu as fait du bon travail.
-papa|C'est le matin. On a brossé.
+papa|Le matin, on a brossé.
 enfant-f|Avec toi.
 papa|Oui. Avec un adulte.
+narrateur|Victorina regarde le miroir.
+narrateur|Ses dents sont propres.
+enfant-f|Elles brillent un peu.
+papa|Oui. Bravo.
 narrateur|Plus tard, le soir arrive.
 narrateur|La veilleuse se rallume.
 narrateur|La lune est plus ronde.
@@ -1407,7 +1410,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa se &lt;emphasis level="moderate"&gt;brosse&lt;/emphasis&gt; les dents. Avec quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1595,7 +1598,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa a pris la brosse. Elle brosse avec l'adulte. C'est papa. &lt;emphasis level="moderate"&gt;matin&lt;/emphasis&gt; et soir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir. Tu te souviens ? Matin et soir. Oui. Avec papa. Bravo. C'est le bon geste. La veilleuse fait encore son rond. Le pyjama à étoiles attend.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1774,7 +1777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa se rince la bouche. Elle dit merci à papa. Les dents brillent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina se rince la bouche. L'eau est fraîche. Merci, papa. Tes dents brillent. Tu as fini ? Oui. Bravo. On va au lit. Le pyjama à étoiles l'attend. La lune est à la fenêtre. Le tapis est encore doux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1941,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Victorina a brossé le matin. Victorina a brossé le soir. Avec papa. Avec la brosse. Bravo, Victorina. L'histoire est finie.</t>
+          <t>Victorina a brossé le matin. Victorina a brossé le soir. Avec papa. Avec la brosse. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a brossé le matin. Victorina a brossé le soir. Avec papa. Avec la brosse. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2084,8 +2087,7 @@
           <t>narrateur|Victorina a brossé le matin.
 narrateur|Victorina a brossé le soir.
 narrateur|Avec papa. Avec la brosse.
-papa|Bravo, Victorina.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Victorina.</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2151,6 +2153,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, papa</t>
+          <t>Victorina, papa</t>
         </is>
       </c>
     </row>
